--- a/8上-下单词表.xlsx
+++ b/8上-下单词表.xlsx
@@ -15642,7 +15642,7 @@
         <v>261</v>
       </c>
       <c r="N262" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263" ht="30" customHeight="1">
@@ -16106,7 +16106,7 @@
         <v>269</v>
       </c>
       <c r="N270" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271" ht="30" customHeight="1">
@@ -16280,7 +16280,7 @@
         <v>272</v>
       </c>
       <c r="N273" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274" ht="30" customHeight="1">
@@ -16454,7 +16454,7 @@
         <v>275</v>
       </c>
       <c r="N276" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277" ht="30" customHeight="1">
@@ -17440,7 +17440,7 @@
         <v>292</v>
       </c>
       <c r="N293" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="294" ht="30" customHeight="1">
@@ -17498,7 +17498,7 @@
         <v>293</v>
       </c>
       <c r="N294" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295" ht="30" customHeight="1">
@@ -17846,7 +17846,7 @@
         <v>299</v>
       </c>
       <c r="N300" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301" ht="30" customHeight="1">
@@ -18020,7 +18020,7 @@
         <v>302</v>
       </c>
       <c r="N303" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304" ht="30" customHeight="1">
@@ -18078,7 +18078,7 @@
         <v>303</v>
       </c>
       <c r="N304" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305" ht="30" customHeight="1">
@@ -19586,7 +19586,7 @@
         <v>329</v>
       </c>
       <c r="N330" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331" ht="30" customHeight="1">
@@ -20746,7 +20746,7 @@
         <v>349</v>
       </c>
       <c r="N350" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="351" ht="30" customHeight="1">
@@ -21210,7 +21210,7 @@
         <v>357</v>
       </c>
       <c r="N358" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="359" ht="30" customHeight="1">
@@ -21442,7 +21442,7 @@
         <v>361</v>
       </c>
       <c r="N362" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="363" ht="30" customHeight="1">
@@ -21558,7 +21558,7 @@
         <v>363</v>
       </c>
       <c r="N364" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365" ht="30" customHeight="1">
@@ -21848,7 +21848,7 @@
         <v>368</v>
       </c>
       <c r="N369" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="370" ht="30" customHeight="1">
@@ -23066,7 +23066,7 @@
         <v>389</v>
       </c>
       <c r="N390" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="391" ht="30" customHeight="1">
@@ -24284,7 +24284,7 @@
         <v>410</v>
       </c>
       <c r="N411" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412" ht="30" customHeight="1">
@@ -24458,7 +24458,7 @@
         <v>413</v>
       </c>
       <c r="N414" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="415" ht="30" customHeight="1">
@@ -24516,7 +24516,7 @@
         <v>414</v>
       </c>
       <c r="N415" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="416" ht="30" customHeight="1">
@@ -24864,7 +24864,7 @@
         <v>420</v>
       </c>
       <c r="N421" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="422" ht="30" customHeight="1">
@@ -25734,7 +25734,7 @@
         <v>435</v>
       </c>
       <c r="N436" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="437" ht="30" customHeight="1">
@@ -25850,7 +25850,7 @@
         <v>437</v>
       </c>
       <c r="N438" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="439" ht="30" customHeight="1">
@@ -26024,7 +26024,7 @@
         <v>440</v>
       </c>
       <c r="N441" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="442" ht="30" customHeight="1">
@@ -26082,7 +26082,7 @@
         <v>441</v>
       </c>
       <c r="N442" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="443" ht="30" customHeight="1">
@@ -27126,7 +27126,7 @@
         <v>459</v>
       </c>
       <c r="N460" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="461" ht="30" customHeight="1">
@@ -27648,7 +27648,7 @@
         <v>468</v>
       </c>
       <c r="N469" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="470" ht="30" customHeight="1">
@@ -27764,7 +27764,7 @@
         <v>470</v>
       </c>
       <c r="N471" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="472" ht="30" customHeight="1">
@@ -27822,7 +27822,7 @@
         <v>471</v>
       </c>
       <c r="N472" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="473" ht="30" customHeight="1">
@@ -27880,7 +27880,7 @@
         <v>472</v>
       </c>
       <c r="N473" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="474" ht="30" customHeight="1">
@@ -28112,7 +28112,7 @@
         <v>476</v>
       </c>
       <c r="N477" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="478" ht="30" customHeight="1">
@@ -28518,7 +28518,7 @@
         <v>483</v>
       </c>
       <c r="N484" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="485" ht="30" customHeight="1">
@@ -28750,7 +28750,7 @@
         <v>487</v>
       </c>
       <c r="N488" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="489" ht="30" customHeight="1">
@@ -28808,7 +28808,7 @@
         <v>488</v>
       </c>
       <c r="N489" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="490" ht="30" customHeight="1">
@@ -29442,7 +29442,7 @@
         <v>499</v>
       </c>
       <c r="N500" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="501" ht="30" customHeight="1">
@@ -29674,7 +29674,7 @@
         <v>503</v>
       </c>
       <c r="N504" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="505" ht="30" customHeight="1">
@@ -29790,7 +29790,7 @@
         <v>505</v>
       </c>
       <c r="N506" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="507" ht="30" customHeight="1">
@@ -29964,7 +29964,7 @@
         <v>508</v>
       </c>
       <c r="N509" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="510" ht="30" customHeight="1">
@@ -30022,7 +30022,7 @@
         <v>509</v>
       </c>
       <c r="N510" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="511" ht="30" customHeight="1">
@@ -30080,7 +30080,7 @@
         <v>510</v>
       </c>
       <c r="N511" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="512" ht="30" customHeight="1">
@@ -30254,7 +30254,7 @@
         <v>513</v>
       </c>
       <c r="N514" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="515" ht="30" customHeight="1">
@@ -30370,7 +30370,7 @@
         <v>515</v>
       </c>
       <c r="N516" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="517" ht="30" customHeight="1">
@@ -30428,7 +30428,7 @@
         <v>516</v>
       </c>
       <c r="N517" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="518" ht="30" customHeight="1">
@@ -30486,7 +30486,7 @@
         <v>517</v>
       </c>
       <c r="N518" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="519" ht="30" customHeight="1">
@@ -30602,7 +30602,7 @@
         <v>519</v>
       </c>
       <c r="N520" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="521" ht="30" customHeight="1">
@@ -30776,7 +30776,7 @@
         <v>522</v>
       </c>
       <c r="N523" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="524" ht="30" customHeight="1">
@@ -30834,7 +30834,7 @@
         <v>523</v>
       </c>
       <c r="N524" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="525" ht="30" customHeight="1">
@@ -30892,7 +30892,7 @@
         <v>524</v>
       </c>
       <c r="N525" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="526" ht="30" customHeight="1">
@@ -31008,7 +31008,7 @@
         <v>526</v>
       </c>
       <c r="N527" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="528" ht="30" customHeight="1">
@@ -31066,7 +31066,7 @@
         <v>527</v>
       </c>
       <c r="N528" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="529" ht="30" customHeight="1">
@@ -31124,7 +31124,7 @@
         <v>528</v>
       </c>
       <c r="N529" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="530" ht="30" customHeight="1">
@@ -31240,7 +31240,7 @@
         <v>530</v>
       </c>
       <c r="N531" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="532" ht="30" customHeight="1">
@@ -31298,7 +31298,7 @@
         <v>531</v>
       </c>
       <c r="N532" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="533" ht="30" customHeight="1">
@@ -31472,7 +31472,7 @@
         <v>534</v>
       </c>
       <c r="N535" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="536" ht="30" customHeight="1">
@@ -31646,7 +31646,7 @@
         <v>537</v>
       </c>
       <c r="N538" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="539" ht="30" customHeight="1">
@@ -31704,7 +31704,7 @@
         <v>538</v>
       </c>
       <c r="N539" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="540" ht="30" customHeight="1">
@@ -31762,7 +31762,7 @@
         <v>539</v>
       </c>
       <c r="N540" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="541" ht="30" customHeight="1">
@@ -31820,7 +31820,7 @@
         <v>540</v>
       </c>
       <c r="N541" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="542" ht="30" customHeight="1">
@@ -31936,7 +31936,7 @@
         <v>542</v>
       </c>
       <c r="N543" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="544" ht="30" customHeight="1">
@@ -32110,7 +32110,7 @@
         <v>545</v>
       </c>
       <c r="N546" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="547" ht="30" customHeight="1">
@@ -32226,7 +32226,7 @@
         <v>547</v>
       </c>
       <c r="N548" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="549" ht="30" customHeight="1">
@@ -32284,7 +32284,7 @@
         <v>548</v>
       </c>
       <c r="N549" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="550" ht="30" customHeight="1">
@@ -32342,7 +32342,7 @@
         <v>549</v>
       </c>
       <c r="N550" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="551" ht="30" customHeight="1">
@@ -32400,7 +32400,7 @@
         <v>550</v>
       </c>
       <c r="N551" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="552" ht="30" customHeight="1">
@@ -32516,7 +32516,7 @@
         <v>552</v>
       </c>
       <c r="N553" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="554" ht="30" customHeight="1">
@@ -32632,7 +32632,7 @@
         <v>554</v>
       </c>
       <c r="N555" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="556" ht="30" customHeight="1">
@@ -32690,7 +32690,7 @@
         <v>555</v>
       </c>
       <c r="N556" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="557" ht="30" customHeight="1">
@@ -32748,7 +32748,7 @@
         <v>556</v>
       </c>
       <c r="N557" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="558" ht="30" customHeight="1">
@@ -32806,7 +32806,7 @@
         <v>557</v>
       </c>
       <c r="N558" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="559" ht="30" customHeight="1">
@@ -32864,7 +32864,7 @@
         <v>558</v>
       </c>
       <c r="N559" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="560" ht="30" customHeight="1">
@@ -32922,7 +32922,7 @@
         <v>559</v>
       </c>
       <c r="N560" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="561" ht="30" customHeight="1">
@@ -32980,7 +32980,7 @@
         <v>560</v>
       </c>
       <c r="N561" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="562" ht="30" customHeight="1">
@@ -33038,7 +33038,7 @@
         <v>561</v>
       </c>
       <c r="N562" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="563" ht="30" customHeight="1">
@@ -33096,7 +33096,7 @@
         <v>562</v>
       </c>
       <c r="N563" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="564" ht="30" customHeight="1">
@@ -33154,7 +33154,7 @@
         <v>563</v>
       </c>
       <c r="N564" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="565" ht="30" customHeight="1">
@@ -33212,7 +33212,7 @@
         <v>564</v>
       </c>
       <c r="N565" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="566" ht="30" customHeight="1">
@@ -33270,7 +33270,7 @@
         <v>565</v>
       </c>
       <c r="N566" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="567" ht="30" customHeight="1">
@@ -33328,7 +33328,7 @@
         <v>566</v>
       </c>
       <c r="N567" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="568" ht="30" customHeight="1">
@@ -33386,7 +33386,7 @@
         <v>567</v>
       </c>
       <c r="N568" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="569" ht="30" customHeight="1">
@@ -33444,7 +33444,7 @@
         <v>568</v>
       </c>
       <c r="N569" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="570" ht="30" customHeight="1">
@@ -33502,7 +33502,7 @@
         <v>569</v>
       </c>
       <c r="N570" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="571" ht="30" customHeight="1">
@@ -33560,7 +33560,7 @@
         <v>570</v>
       </c>
       <c r="N571" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="572" ht="30" customHeight="1">
@@ -33618,7 +33618,7 @@
         <v>571</v>
       </c>
       <c r="N572" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="573" ht="30" customHeight="1">
@@ -33676,7 +33676,7 @@
         <v>572</v>
       </c>
       <c r="N573" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="574" ht="30" customHeight="1">
@@ -33792,7 +33792,7 @@
         <v>574</v>
       </c>
       <c r="N575" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="576" ht="30" customHeight="1">
@@ -33850,7 +33850,7 @@
         <v>575</v>
       </c>
       <c r="N576" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="577" ht="30" customHeight="1">
@@ -33908,7 +33908,7 @@
         <v>576</v>
       </c>
       <c r="N577" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="578" ht="30" customHeight="1">
@@ -33966,7 +33966,7 @@
         <v>577</v>
       </c>
       <c r="N578" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="579" ht="30" customHeight="1">
@@ -34198,7 +34198,7 @@
         <v>581</v>
       </c>
       <c r="N582" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="583" ht="30" customHeight="1">
@@ -34256,7 +34256,7 @@
         <v>582</v>
       </c>
       <c r="N583" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="584" ht="30" customHeight="1">
@@ -34314,7 +34314,7 @@
         <v>583</v>
       </c>
       <c r="N584" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="585" ht="30" customHeight="1">
@@ -34372,7 +34372,7 @@
         <v>584</v>
       </c>
       <c r="N585" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="586" ht="30" customHeight="1">
@@ -34430,7 +34430,7 @@
         <v>585</v>
       </c>
       <c r="N586" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="587" ht="30" customHeight="1">
@@ -34488,7 +34488,7 @@
         <v>586</v>
       </c>
       <c r="N587" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="588" ht="30" customHeight="1">
@@ -34604,7 +34604,7 @@
         <v>588</v>
       </c>
       <c r="N589" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="590" ht="30" customHeight="1">
@@ -34662,7 +34662,7 @@
         <v>589</v>
       </c>
       <c r="N590" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="591" ht="30" customHeight="1">
@@ -35068,7 +35068,7 @@
         <v>596</v>
       </c>
       <c r="N597" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="598" ht="30" customHeight="1">
@@ -35126,7 +35126,7 @@
         <v>597</v>
       </c>
       <c r="N598" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="599" ht="30" customHeight="1">
@@ -35242,7 +35242,7 @@
         <v>599</v>
       </c>
       <c r="N600" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="601" ht="30" customHeight="1">
@@ -35358,7 +35358,7 @@
         <v>601</v>
       </c>
       <c r="N602" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="603" ht="30" customHeight="1">
@@ -35474,7 +35474,7 @@
         <v>603</v>
       </c>
       <c r="N604" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="605" ht="30" customHeight="1">
@@ -36228,7 +36228,7 @@
         <v>616</v>
       </c>
       <c r="N617" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="618" ht="30" customHeight="1">
@@ -36286,7 +36286,7 @@
         <v>617</v>
       </c>
       <c r="N618" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="619" ht="30" customHeight="1">
@@ -36344,7 +36344,7 @@
         <v>618</v>
       </c>
       <c r="N619" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="620" ht="30" customHeight="1">
@@ -36402,7 +36402,7 @@
         <v>619</v>
       </c>
       <c r="N620" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="621" ht="30" customHeight="1">
@@ -36518,7 +36518,7 @@
         <v>621</v>
       </c>
       <c r="N622" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="623" ht="30" customHeight="1">
@@ -36692,7 +36692,7 @@
         <v>624</v>
       </c>
       <c r="N625" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="626" ht="30" customHeight="1">
@@ -36924,7 +36924,7 @@
         <v>628</v>
       </c>
       <c r="N629" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="630" ht="30" customHeight="1">
@@ -37098,7 +37098,7 @@
         <v>631</v>
       </c>
       <c r="N632" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="633" ht="30" customHeight="1">
@@ -37272,7 +37272,7 @@
         <v>634</v>
       </c>
       <c r="N635" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="636" ht="30" customHeight="1">
@@ -37330,7 +37330,7 @@
         <v>635</v>
       </c>
       <c r="N636" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="637" ht="30" customHeight="1">
@@ -37446,7 +37446,7 @@
         <v>637</v>
       </c>
       <c r="N638" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="639" ht="30" customHeight="1">
@@ -37616,7 +37616,7 @@
         <v>640</v>
       </c>
       <c r="N641" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="642" ht="30" customHeight="1">
@@ -37670,7 +37670,7 @@
         <v>641</v>
       </c>
       <c r="N642" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="643" ht="30" customHeight="1">
@@ -37728,7 +37728,7 @@
         <v>642</v>
       </c>
       <c r="N643" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="644" ht="30" customHeight="1">
@@ -37902,7 +37902,7 @@
         <v>645</v>
       </c>
       <c r="N646" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="647" ht="30" customHeight="1">
@@ -37960,7 +37960,7 @@
         <v>646</v>
       </c>
       <c r="N647" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="648" ht="30" customHeight="1">
@@ -38018,7 +38018,7 @@
         <v>647</v>
       </c>
       <c r="N648" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="649" ht="30" customHeight="1">
@@ -38134,7 +38134,7 @@
         <v>649</v>
       </c>
       <c r="N650" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="651" ht="30" customHeight="1">
@@ -38192,7 +38192,7 @@
         <v>650</v>
       </c>
       <c r="N651" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="652" ht="30" customHeight="1">
@@ -38246,7 +38246,7 @@
         <v>651</v>
       </c>
       <c r="N652" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="653" ht="30" customHeight="1">
@@ -38304,7 +38304,7 @@
         <v>652</v>
       </c>
       <c r="N653" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="654" ht="30" customHeight="1">
@@ -38474,7 +38474,7 @@
         <v>655</v>
       </c>
       <c r="N656" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="657" ht="30" customHeight="1">
@@ -38760,7 +38760,7 @@
         <v>660</v>
       </c>
       <c r="N661" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="662" ht="30" customHeight="1">
@@ -38926,7 +38926,7 @@
         <v>663</v>
       </c>
       <c r="N664" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="665" ht="30" customHeight="1">
@@ -39274,7 +39274,7 @@
         <v>669</v>
       </c>
       <c r="N670" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="671" ht="30" customHeight="1">
@@ -39390,7 +39390,7 @@
         <v>671</v>
       </c>
       <c r="N672" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="673" ht="30" customHeight="1">
@@ -39448,7 +39448,7 @@
         <v>672</v>
       </c>
       <c r="N673" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="674" ht="30" customHeight="1">
@@ -39506,7 +39506,7 @@
         <v>673</v>
       </c>
       <c r="N674" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="675" ht="30" customHeight="1">
@@ -39564,7 +39564,7 @@
         <v>674</v>
       </c>
       <c r="N675" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="676" ht="30" customHeight="1">
@@ -39680,7 +39680,7 @@
         <v>676</v>
       </c>
       <c r="N677" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="678" ht="30" customHeight="1">
@@ -39796,7 +39796,7 @@
         <v>678</v>
       </c>
       <c r="N679" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="680" ht="30" customHeight="1">
@@ -39854,7 +39854,7 @@
         <v>679</v>
       </c>
       <c r="N680" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="681" ht="30" customHeight="1">
@@ -39970,7 +39970,7 @@
         <v>681</v>
       </c>
       <c r="N682" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="683" ht="30" customHeight="1">
@@ -40028,7 +40028,7 @@
         <v>682</v>
       </c>
       <c r="N683" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="684" ht="30" customHeight="1">
@@ -40144,7 +40144,7 @@
         <v>684</v>
       </c>
       <c r="N685" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="686" ht="30" customHeight="1">
@@ -40202,7 +40202,7 @@
         <v>685</v>
       </c>
       <c r="N686" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="687" ht="30" customHeight="1">
@@ -40260,7 +40260,7 @@
         <v>686</v>
       </c>
       <c r="N687" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="688" ht="30" customHeight="1">
@@ -40318,7 +40318,7 @@
         <v>687</v>
       </c>
       <c r="N688" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="689" ht="30" customHeight="1">
@@ -40376,7 +40376,7 @@
         <v>688</v>
       </c>
       <c r="N689" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="690" ht="30" customHeight="1">
@@ -40434,7 +40434,7 @@
         <v>689</v>
       </c>
       <c r="N690" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="691" ht="30" customHeight="1">
@@ -40492,7 +40492,7 @@
         <v>690</v>
       </c>
       <c r="N691" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="692" ht="30" customHeight="1">
@@ -40550,7 +40550,7 @@
         <v>691</v>
       </c>
       <c r="N692" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="693" ht="30" customHeight="1">
@@ -40608,7 +40608,7 @@
         <v>692</v>
       </c>
       <c r="N693" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="694" ht="30" customHeight="1">
@@ -40666,7 +40666,7 @@
         <v>693</v>
       </c>
       <c r="N694" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="695" ht="30" customHeight="1">
@@ -40724,7 +40724,7 @@
         <v>694</v>
       </c>
       <c r="N695" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="696" ht="30" customHeight="1">
@@ -40782,7 +40782,7 @@
         <v>695</v>
       </c>
       <c r="N696" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="697" ht="30" customHeight="1">
@@ -40898,7 +40898,7 @@
         <v>697</v>
       </c>
       <c r="N698" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="699" ht="30" customHeight="1">
@@ -40956,7 +40956,7 @@
         <v>698</v>
       </c>
       <c r="N699" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="700" ht="30" customHeight="1">
@@ -41072,7 +41072,7 @@
         <v>700</v>
       </c>
       <c r="N701" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="702" ht="30" customHeight="1">
@@ -41246,7 +41246,7 @@
         <v>703</v>
       </c>
       <c r="N704" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="705" ht="30" customHeight="1">
@@ -41304,7 +41304,7 @@
         <v>704</v>
       </c>
       <c r="N705" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="706" ht="30" customHeight="1">
@@ -41439,7 +41439,7 @@
         <v>7</v>
       </c>
       <c r="E708" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F708" s="3" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>708</v>
       </c>
       <c r="N709" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="710" ht="30" customHeight="1">
@@ -41594,7 +41594,7 @@
         <v>709</v>
       </c>
       <c r="N710" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="711" ht="30" customHeight="1">
@@ -41768,7 +41768,7 @@
         <v>712</v>
       </c>
       <c r="N713" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="714" ht="30" customHeight="1">
@@ -41826,7 +41826,7 @@
         <v>713</v>
       </c>
       <c r="N714" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="715" ht="30" customHeight="1">
@@ -41884,7 +41884,7 @@
         <v>714</v>
       </c>
       <c r="N715" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="716" ht="30" customHeight="1">
@@ -41938,7 +41938,7 @@
         <v>715</v>
       </c>
       <c r="N716" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="717" ht="30" customHeight="1">
@@ -41992,7 +41992,7 @@
         <v>716</v>
       </c>
       <c r="N717" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="718" ht="30" customHeight="1">
@@ -42108,7 +42108,7 @@
         <v>718</v>
       </c>
       <c r="N719" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="720" ht="30" customHeight="1">
@@ -42850,7 +42850,7 @@
         <v>731</v>
       </c>
       <c r="N732" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="733" ht="30" customHeight="1">
@@ -42966,7 +42966,7 @@
         <v>733</v>
       </c>
       <c r="N734" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="735" ht="30" customHeight="1">
@@ -43024,7 +43024,7 @@
         <v>734</v>
       </c>
       <c r="N735" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="736" ht="30" customHeight="1">
@@ -43082,7 +43082,7 @@
         <v>735</v>
       </c>
       <c r="N736" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="737" ht="30" customHeight="1">
@@ -43140,7 +43140,7 @@
         <v>736</v>
       </c>
       <c r="N737" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="738" ht="30" customHeight="1">
@@ -43256,7 +43256,7 @@
         <v>738</v>
       </c>
       <c r="N739" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="740" ht="30" customHeight="1">
@@ -43314,7 +43314,7 @@
         <v>739</v>
       </c>
       <c r="N740" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="741" ht="30" customHeight="1">
@@ -43372,7 +43372,7 @@
         <v>740</v>
       </c>
       <c r="N741" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="742" ht="30" customHeight="1">
@@ -43546,7 +43546,7 @@
         <v>743</v>
       </c>
       <c r="N744" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="745" ht="30" customHeight="1">
@@ -43662,7 +43662,7 @@
         <v>745</v>
       </c>
       <c r="N746" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="747" ht="30" customHeight="1">
@@ -43778,7 +43778,7 @@
         <v>747</v>
       </c>
       <c r="N748" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="749" ht="30" customHeight="1">
@@ -43836,7 +43836,7 @@
         <v>748</v>
       </c>
       <c r="N749" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="750" ht="30" customHeight="1">
@@ -43952,7 +43952,7 @@
         <v>750</v>
       </c>
       <c r="N751" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="752" ht="30" customHeight="1">
@@ -44474,7 +44474,7 @@
         <v>759</v>
       </c>
       <c r="N760" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="761" ht="30" customHeight="1">
@@ -44532,7 +44532,7 @@
         <v>760</v>
       </c>
       <c r="N761" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="762" ht="30" customHeight="1">
@@ -44590,7 +44590,7 @@
         <v>761</v>
       </c>
       <c r="N762" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="763" ht="30" customHeight="1">
@@ -44648,7 +44648,7 @@
         <v>762</v>
       </c>
       <c r="N763" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="764" ht="30" customHeight="1">
@@ -44706,7 +44706,7 @@
         <v>763</v>
       </c>
       <c r="N764" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="765" ht="30" customHeight="1">
@@ -44764,7 +44764,7 @@
         <v>764</v>
       </c>
       <c r="N765" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="766" ht="30" customHeight="1">
@@ -44822,7 +44822,7 @@
         <v>765</v>
       </c>
       <c r="N766" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="767" ht="30" customHeight="1">
@@ -44938,7 +44938,7 @@
         <v>767</v>
       </c>
       <c r="N768" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="769" ht="30" customHeight="1">
@@ -44996,7 +44996,7 @@
         <v>768</v>
       </c>
       <c r="N769" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="770" ht="30" customHeight="1">
@@ -45054,7 +45054,7 @@
         <v>769</v>
       </c>
       <c r="N770" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="771" ht="30" customHeight="1">
@@ -45112,7 +45112,7 @@
         <v>770</v>
       </c>
       <c r="N771" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="772" ht="30" customHeight="1">
@@ -45170,7 +45170,7 @@
         <v>771</v>
       </c>
       <c r="N772" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="773" ht="30" customHeight="1">
@@ -45228,7 +45228,7 @@
         <v>772</v>
       </c>
       <c r="N773" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="774" ht="30" customHeight="1">
@@ -45286,7 +45286,7 @@
         <v>773</v>
       </c>
       <c r="N774" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="775" ht="30" customHeight="1">
@@ -45344,7 +45344,7 @@
         <v>774</v>
       </c>
       <c r="N775" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="776" ht="30" customHeight="1">
@@ -45402,7 +45402,7 @@
         <v>775</v>
       </c>
       <c r="N776" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="777" ht="30" customHeight="1">
@@ -45460,7 +45460,7 @@
         <v>776</v>
       </c>
       <c r="N777" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="778" ht="30" customHeight="1">
@@ -45518,7 +45518,7 @@
         <v>777</v>
       </c>
       <c r="N778" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="779" ht="30" customHeight="1">
@@ -45576,7 +45576,7 @@
         <v>778</v>
       </c>
       <c r="N779" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="780" ht="30" customHeight="1">
@@ -45634,7 +45634,7 @@
         <v>779</v>
       </c>
       <c r="N780" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="781" ht="30" customHeight="1">
@@ -45692,7 +45692,7 @@
         <v>780</v>
       </c>
       <c r="N781" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="782" ht="30" customHeight="1">
@@ -45750,7 +45750,7 @@
         <v>781</v>
       </c>
       <c r="N782" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="783" ht="30" customHeight="1">
@@ -45808,7 +45808,7 @@
         <v>782</v>
       </c>
       <c r="N783" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="784" ht="30" customHeight="1">
@@ -45866,7 +45866,7 @@
         <v>783</v>
       </c>
       <c r="N784" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="785" ht="30" customHeight="1">
@@ -45924,7 +45924,7 @@
         <v>784</v>
       </c>
       <c r="N785" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="786" ht="30" customHeight="1">
@@ -45982,7 +45982,7 @@
         <v>785</v>
       </c>
       <c r="N786" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="787" ht="30" customHeight="1">
@@ -46040,7 +46040,7 @@
         <v>786</v>
       </c>
       <c r="N787" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="788" ht="30" customHeight="1">
@@ -46098,7 +46098,7 @@
         <v>787</v>
       </c>
       <c r="N788" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="789" ht="30" customHeight="1">
@@ -46156,7 +46156,7 @@
         <v>788</v>
       </c>
       <c r="N789" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="790" ht="30" customHeight="1">
@@ -46214,7 +46214,7 @@
         <v>789</v>
       </c>
       <c r="N790" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="791" ht="30" customHeight="1">
@@ -46446,7 +46446,7 @@
         <v>793</v>
       </c>
       <c r="N794" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="795" ht="30" customHeight="1">
@@ -46504,7 +46504,7 @@
         <v>794</v>
       </c>
       <c r="N795" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="796" ht="30" customHeight="1">
@@ -46562,7 +46562,7 @@
         <v>795</v>
       </c>
       <c r="N796" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="797" ht="30" customHeight="1">
@@ -46620,7 +46620,7 @@
         <v>796</v>
       </c>
       <c r="N797" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="798" ht="30" customHeight="1">
@@ -46678,7 +46678,7 @@
         <v>797</v>
       </c>
       <c r="N798" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="799" ht="30" customHeight="1">
@@ -46736,7 +46736,7 @@
         <v>798</v>
       </c>
       <c r="N799" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="800" ht="30" customHeight="1">
@@ -46794,7 +46794,7 @@
         <v>799</v>
       </c>
       <c r="N800" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="801" ht="30" customHeight="1">
@@ -46852,7 +46852,7 @@
         <v>800</v>
       </c>
       <c r="N801" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="802" ht="30" customHeight="1">
@@ -46910,7 +46910,7 @@
         <v>801</v>
       </c>
       <c r="N802" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="803" ht="30" customHeight="1">
@@ -46968,7 +46968,7 @@
         <v>802</v>
       </c>
       <c r="N803" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="804" ht="30" customHeight="1">
@@ -47026,7 +47026,7 @@
         <v>803</v>
       </c>
       <c r="N804" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="805" ht="30" customHeight="1">
@@ -47084,7 +47084,7 @@
         <v>804</v>
       </c>
       <c r="N805" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="806" ht="30" customHeight="1">
@@ -47142,7 +47142,7 @@
         <v>805</v>
       </c>
       <c r="N806" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="807" ht="30" customHeight="1">
@@ -47200,7 +47200,7 @@
         <v>806</v>
       </c>
       <c r="N807" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="808" ht="30" customHeight="1">
@@ -47258,7 +47258,7 @@
         <v>807</v>
       </c>
       <c r="N808" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="809" ht="30" customHeight="1">
@@ -47316,7 +47316,7 @@
         <v>808</v>
       </c>
       <c r="N809" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="810" ht="30" customHeight="1">
@@ -47374,7 +47374,7 @@
         <v>809</v>
       </c>
       <c r="N810" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="811" ht="30" customHeight="1">
@@ -47432,7 +47432,7 @@
         <v>810</v>
       </c>
       <c r="N811" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="812" ht="30" customHeight="1">
@@ -47490,7 +47490,7 @@
         <v>811</v>
       </c>
       <c r="N812" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="813" ht="30" customHeight="1">
@@ -47548,7 +47548,7 @@
         <v>812</v>
       </c>
       <c r="N813" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="814" ht="30" customHeight="1">
@@ -47606,7 +47606,7 @@
         <v>813</v>
       </c>
       <c r="N814" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="815" ht="30" customHeight="1">
@@ -47722,7 +47722,7 @@
         <v>815</v>
       </c>
       <c r="N816" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="817" ht="30" customHeight="1">
@@ -47780,7 +47780,7 @@
         <v>816</v>
       </c>
       <c r="N817" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="818" ht="30" customHeight="1">
@@ -47838,7 +47838,7 @@
         <v>817</v>
       </c>
       <c r="N818" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="819" ht="30" customHeight="1">
@@ -47896,7 +47896,7 @@
         <v>818</v>
       </c>
       <c r="N819" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="820" ht="30" customHeight="1">
